--- a/bin/exam.xlsx
+++ b/bin/exam.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\prg\GGRM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\prg\GGRM\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -16,6 +16,7 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <calcPr calcId="152511"/>
   <extLst>
@@ -104,7 +105,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -326,6 +338,222 @@
           </cell>
         </row>
       </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="doctor"/>
+      <sheetName val="speciality"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="A2">
+            <v>1</v>
+          </cell>
+          <cell r="B2">
+            <v>1907</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>2</v>
+          </cell>
+          <cell r="B3">
+            <v>1521</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>3</v>
+          </cell>
+          <cell r="B4">
+            <v>350</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>4</v>
+          </cell>
+          <cell r="B5">
+            <v>1050</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>5</v>
+          </cell>
+          <cell r="B6">
+            <v>854</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>6</v>
+          </cell>
+          <cell r="B7">
+            <v>1698</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>7</v>
+          </cell>
+          <cell r="B8">
+            <v>230</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>8</v>
+          </cell>
+          <cell r="B9">
+            <v>1429</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>9</v>
+          </cell>
+          <cell r="B10">
+            <v>284</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>10</v>
+          </cell>
+          <cell r="B11">
+            <v>617</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>11</v>
+          </cell>
+          <cell r="B12">
+            <v>542</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>12</v>
+          </cell>
+          <cell r="B13">
+            <v>863</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>13</v>
+          </cell>
+          <cell r="B14">
+            <v>1165</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>14</v>
+          </cell>
+          <cell r="B15">
+            <v>1625</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>15</v>
+          </cell>
+          <cell r="B16">
+            <v>470</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>16</v>
+          </cell>
+          <cell r="B17">
+            <v>1819</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>17</v>
+          </cell>
+          <cell r="B18">
+            <v>1110</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>18</v>
+          </cell>
+          <cell r="B19">
+            <v>1169</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>19</v>
+          </cell>
+          <cell r="B20">
+            <v>1558</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>20</v>
+          </cell>
+          <cell r="B21">
+            <v>191</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>21</v>
+          </cell>
+          <cell r="B22">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>22</v>
+          </cell>
+          <cell r="B23">
+            <v>56</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>23</v>
+          </cell>
+          <cell r="B24">
+            <v>1188</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>24</v>
+          </cell>
+          <cell r="B25">
+            <v>1953</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>25</v>
+          </cell>
+          <cell r="B26">
+            <v>377</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -634,30 +862,30 @@
       </c>
       <c r="C2">
         <f ca="1">VLOOKUP(G2,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1362</v>
+        <v>1401</v>
       </c>
       <c r="D2">
-        <f ca="1">VLOOKUP(H2,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1079</v>
+        <f ca="1">VLOOKUP(H2,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>377</v>
       </c>
       <c r="E2" s="1">
         <v>45716</v>
       </c>
       <c r="F2">
         <f ca="1">ROUNDUP(RAND()*100,0)</f>
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="G2">
         <f ca="1">ROUNDUP(RAND()*25,0)</f>
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H2">
         <f ca="1">ROUNDUP(RAND()*25,0)</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I2" t="str">
         <f ca="1">CONCATENATE("(",B2, ", ", C2,", ", D2, ", ", CHAR(39), TEXT(E2, "yyyy-mm-dd"), CHAR(39), ", ", F2, "),")</f>
-        <v>(457, 1362, 1079, '2025-02-28', 32),</v>
+        <v>(457, 1401, 377, '2025-02-28', 94),</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -669,30 +897,30 @@
       </c>
       <c r="C3">
         <f ca="1">VLOOKUP(G3,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>83</v>
+        <v>1992</v>
       </c>
       <c r="D3">
-        <f ca="1">VLOOKUP(H3,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1674</v>
+        <f ca="1">VLOOKUP(H3,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>1110</v>
       </c>
       <c r="E3" s="1">
         <v>45721</v>
       </c>
       <c r="F3">
         <f t="shared" ref="F3:F26" ca="1" si="0">ROUNDUP(RAND()*100,0)</f>
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G3">
         <f t="shared" ref="G3:H26" ca="1" si="1">ROUNDUP(RAND()*25,0)</f>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H3">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I3" t="str">
         <f t="shared" ref="I3:I26" ca="1" si="2">CONCATENATE("(",B3, ", ", C3,", ", D3, ", ", CHAR(39), TEXT(E3, "yyyy-mm-dd"), CHAR(39), ", ", F3, "),")</f>
-        <v>(847, 83, 1674, '2025-03-05', 23),</v>
+        <v>(847, 1992, 1110, '2025-03-05', 32),</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -704,30 +932,30 @@
       </c>
       <c r="C4">
         <f ca="1">VLOOKUP(G4,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1884</v>
+        <v>717</v>
       </c>
       <c r="D4">
-        <f ca="1">VLOOKUP(H4,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1896</v>
+        <f ca="1">VLOOKUP(H4,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>350</v>
       </c>
       <c r="E4" s="1">
         <v>45722</v>
       </c>
       <c r="F4">
         <f t="shared" ca="1" si="0"/>
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="G4">
         <f t="shared" ca="1" si="1"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(235, 1884, 1896, '2025-03-06', 85),</v>
+        <v>(235, 717, 350, '2025-03-06', 51),</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -739,30 +967,30 @@
       </c>
       <c r="C5">
         <f ca="1">VLOOKUP(G5,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>83</v>
+        <v>1992</v>
       </c>
       <c r="D5">
-        <f ca="1">VLOOKUP(H5,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1520</v>
+        <f ca="1">VLOOKUP(H5,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>1698</v>
       </c>
       <c r="E5" s="1">
         <v>45735</v>
       </c>
       <c r="F5">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="G5">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H5">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I5" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(946, 83, 1520, '2025-03-19', 81),</v>
+        <v>(946, 1992, 1698, '2025-03-19', 40),</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -774,22 +1002,22 @@
       </c>
       <c r="C6">
         <f ca="1">VLOOKUP(G6,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>638</v>
+        <v>1341</v>
       </c>
       <c r="D6">
-        <f ca="1">VLOOKUP(H6,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1401</v>
+        <f ca="1">VLOOKUP(H6,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>230</v>
       </c>
       <c r="E6" s="1">
         <v>45747</v>
       </c>
       <c r="F6">
         <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <f t="shared" ca="1" si="1"/>
@@ -797,7 +1025,7 @@
       </c>
       <c r="I6" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1667, 638, 1401, '2025-03-31', 32),</v>
+        <v>(1667, 1341, 230, '2025-03-31', 100),</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -809,30 +1037,30 @@
       </c>
       <c r="C7">
         <f ca="1">VLOOKUP(G7,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1773</v>
+        <v>1674</v>
       </c>
       <c r="D7">
-        <f ca="1">VLOOKUP(H7,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>92</v>
+        <f ca="1">VLOOKUP(H7,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>542</v>
       </c>
       <c r="E7" s="1">
         <v>45761</v>
       </c>
       <c r="F7">
         <f t="shared" ca="1" si="0"/>
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="G7">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H7">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(562, 1773, 92, '2025-04-14', 53),</v>
+        <v>(562, 1674, 542, '2025-04-14', 37),</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -844,30 +1072,30 @@
       </c>
       <c r="C8">
         <f ca="1">VLOOKUP(G8,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>723</v>
+        <v>1520</v>
       </c>
       <c r="D8">
-        <f ca="1">VLOOKUP(H8,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1674</v>
+        <f ca="1">VLOOKUP(H8,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>1188</v>
       </c>
       <c r="E8" s="1">
         <v>45764</v>
       </c>
       <c r="F8">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H8">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="I8" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(83, 723, 1674, '2025-04-17', 8),</v>
+        <v>(83, 1520, 1188, '2025-04-17', 62),</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -879,30 +1107,30 @@
       </c>
       <c r="C9">
         <f ca="1">VLOOKUP(G9,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>804</v>
+        <v>346</v>
       </c>
       <c r="D9">
-        <f ca="1">VLOOKUP(H9,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1674</v>
+        <f ca="1">VLOOKUP(H9,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>1953</v>
       </c>
       <c r="E9" s="1">
         <v>45803</v>
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="G9">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H9">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(427, 804, 1674, '2025-05-26', 35),</v>
+        <v>(427, 346, 1953, '2025-05-26', 72),</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -914,30 +1142,30 @@
       </c>
       <c r="C10">
         <f ca="1">VLOOKUP(G10,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1992</v>
+        <v>1401</v>
       </c>
       <c r="D10">
-        <f ca="1">VLOOKUP(H10,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>123</v>
+        <f ca="1">VLOOKUP(H10,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>377</v>
       </c>
       <c r="E10" s="1">
         <v>45859</v>
       </c>
       <c r="F10">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G10">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H10">
         <f t="shared" ca="1" si="1"/>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1115, 1992, 123, '2025-07-21', 19),</v>
+        <v>(1115, 1401, 377, '2025-07-21', 35),</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -949,30 +1177,30 @@
       </c>
       <c r="C11">
         <f ca="1">VLOOKUP(G11,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1362</v>
+        <v>222</v>
       </c>
       <c r="D11">
-        <f ca="1">VLOOKUP(H11,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1091</v>
+        <f ca="1">VLOOKUP(H11,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>1429</v>
       </c>
       <c r="E11" s="1">
         <v>45868</v>
       </c>
       <c r="F11">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="G11">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1411, 1362, 1091, '2025-07-30', 13),</v>
+        <v>(1411, 222, 1429, '2025-07-30', 98),</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -984,30 +1212,30 @@
       </c>
       <c r="C12">
         <f ca="1">VLOOKUP(G12,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>83</v>
+        <v>1520</v>
       </c>
       <c r="D12">
-        <f ca="1">VLOOKUP(H12,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1992</v>
+        <f ca="1">VLOOKUP(H12,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>377</v>
       </c>
       <c r="E12" s="1">
         <v>45891</v>
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="0"/>
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="G12">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H12">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="I12" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(909, 83, 1992, '2025-08-22', 98),</v>
+        <v>(909, 1520, 377, '2025-08-22', 2),</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1019,30 +1247,30 @@
       </c>
       <c r="C13">
         <f ca="1">VLOOKUP(G13,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>804</v>
+        <v>92</v>
       </c>
       <c r="D13">
-        <f ca="1">VLOOKUP(H13,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>92</v>
+        <f ca="1">VLOOKUP(H13,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>1169</v>
       </c>
       <c r="E13" s="1">
         <v>45898</v>
       </c>
       <c r="F13">
         <f t="shared" ca="1" si="0"/>
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H13">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1463, 804, 92, '2025-08-29', 6),</v>
+        <v>(1463, 92, 1169, '2025-08-29', 100),</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1054,30 +1282,30 @@
       </c>
       <c r="C14">
         <f ca="1">VLOOKUP(G14,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>717</v>
+        <v>346</v>
       </c>
       <c r="D14">
-        <f ca="1">VLOOKUP(H14,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1362</v>
+        <f ca="1">VLOOKUP(H14,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>1819</v>
       </c>
       <c r="E14" s="1">
         <v>45944</v>
       </c>
       <c r="F14">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <f t="shared" ca="1" si="1"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H14">
         <f t="shared" ca="1" si="1"/>
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I14" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(201, 717, 1362, '2025-10-14', 12),</v>
+        <v>(201, 346, 1819, '2025-10-14', 10),</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1089,30 +1317,30 @@
       </c>
       <c r="C15">
         <f ca="1">VLOOKUP(G15,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="D15">
-        <f ca="1">VLOOKUP(H15,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>222</v>
+        <f ca="1">VLOOKUP(H15,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>350</v>
       </c>
       <c r="E15" s="1">
         <v>45972</v>
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="G15">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H15">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I15" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(480, 92, 222, '2025-11-11', 8),</v>
+        <v>(480, 50, 350, '2025-11-11', 37),</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1124,30 +1352,30 @@
       </c>
       <c r="C16">
         <f ca="1">VLOOKUP(G16,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1091</v>
+        <v>1992</v>
       </c>
       <c r="D16">
-        <f ca="1">VLOOKUP(H16,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>92</v>
+        <f ca="1">VLOOKUP(H16,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>1907</v>
       </c>
       <c r="E16" s="1">
         <v>45975</v>
       </c>
       <c r="F16">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G16">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H16">
         <f t="shared" ca="1" si="1"/>
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I16" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1291, 1091, 92, '2025-11-14', 40),</v>
+        <v>(1291, 1992, 1907, '2025-11-14', 25),</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1159,30 +1387,30 @@
       </c>
       <c r="C17">
         <f ca="1">VLOOKUP(G17,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1341</v>
+        <v>123</v>
       </c>
       <c r="D17">
-        <f ca="1">VLOOKUP(H17,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>804</v>
+        <f ca="1">VLOOKUP(H17,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>1165</v>
       </c>
       <c r="E17" s="1">
         <v>45999</v>
       </c>
       <c r="F17">
         <f t="shared" ca="1" si="0"/>
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="G17">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H17">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I17" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1520, 1341, 804, '2025-12-08', 93),</v>
+        <v>(1520, 123, 1165, '2025-12-08', 42),</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1194,30 +1422,30 @@
       </c>
       <c r="C18">
         <f ca="1">VLOOKUP(G18,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1343</v>
+        <v>717</v>
       </c>
       <c r="D18">
-        <f ca="1">VLOOKUP(H18,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1341</v>
+        <f ca="1">VLOOKUP(H18,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>1558</v>
       </c>
       <c r="E18" s="1">
         <v>46087</v>
       </c>
       <c r="F18">
         <f t="shared" ca="1" si="0"/>
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G18">
         <f t="shared" ca="1" si="1"/>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H18">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(656, 1343, 1341, '2026-03-06', 27),</v>
+        <v>(656, 717, 1558, '2026-03-06', 77),</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1229,30 +1457,30 @@
       </c>
       <c r="C19">
         <f ca="1">VLOOKUP(G19,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>723</v>
+        <v>1341</v>
       </c>
       <c r="D19">
-        <f ca="1">VLOOKUP(H19,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>83</v>
+        <f ca="1">VLOOKUP(H19,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>1050</v>
       </c>
       <c r="E19" s="1">
         <v>46106</v>
       </c>
       <c r="F19">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="G19">
         <f t="shared" ca="1" si="1"/>
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H19">
         <f t="shared" ca="1" si="1"/>
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1914, 723, 83, '2026-03-25', 5),</v>
+        <v>(1914, 1341, 1050, '2026-03-25', 56),</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1264,30 +1492,30 @@
       </c>
       <c r="C20">
         <f ca="1">VLOOKUP(G20,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>548</v>
+        <v>1992</v>
       </c>
       <c r="D20">
-        <f ca="1">VLOOKUP(H20,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1520</v>
+        <f ca="1">VLOOKUP(H20,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>1819</v>
       </c>
       <c r="E20" s="1">
         <v>46112</v>
       </c>
       <c r="F20">
         <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G20">
+        <f t="shared" ca="1" si="1"/>
         <v>9</v>
       </c>
-      <c r="G20">
-        <f t="shared" ca="1" si="1"/>
-        <v>6</v>
-      </c>
       <c r="H20">
         <f t="shared" ca="1" si="1"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I20" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(627, 548, 1520, '2026-03-31', 9),</v>
+        <v>(627, 1992, 1819, '2026-03-31', 10),</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1299,30 +1527,30 @@
       </c>
       <c r="C21">
         <f ca="1">VLOOKUP(G21,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>222</v>
+        <v>1896</v>
       </c>
       <c r="D21">
-        <f ca="1">VLOOKUP(H21,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1091</v>
+        <f ca="1">VLOOKUP(H21,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>230</v>
       </c>
       <c r="E21" s="1">
         <v>46139</v>
       </c>
       <c r="F21">
         <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="G21">
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="H21">
+        <f t="shared" ca="1" si="1"/>
         <v>7</v>
       </c>
-      <c r="G21">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="H21">
-        <f t="shared" ca="1" si="1"/>
-        <v>23</v>
-      </c>
       <c r="I21" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1501, 222, 1091, '2026-04-27', 7),</v>
+        <v>(1501, 1896, 230, '2026-04-27', 15),</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1334,30 +1562,30 @@
       </c>
       <c r="C22">
         <f ca="1">VLOOKUP(G22,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1341</v>
+        <v>1362</v>
       </c>
       <c r="D22">
-        <f ca="1">VLOOKUP(H22,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1773</v>
+        <f ca="1">VLOOKUP(H22,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>1110</v>
       </c>
       <c r="E22" s="1">
         <v>46169</v>
       </c>
       <c r="F22">
         <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G22">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="H22">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I22" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1478, 1341, 1773, '2026-05-27', 39),</v>
+        <v>(1478, 1362, 1110, '2026-05-27', 33),</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1369,30 +1597,30 @@
       </c>
       <c r="C23">
         <f ca="1">VLOOKUP(G23,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1091</v>
+        <v>1520</v>
       </c>
       <c r="D23">
-        <f ca="1">VLOOKUP(H23,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>638</v>
+        <f ca="1">VLOOKUP(H23,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>284</v>
       </c>
       <c r="E23" s="1">
         <v>46230</v>
       </c>
       <c r="F23">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="G23">
         <f t="shared" ca="1" si="1"/>
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H23">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I23" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(799, 1091, 638, '2026-07-27', 20),</v>
+        <v>(799, 1520, 284, '2026-07-27', 84),</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1404,30 +1632,30 @@
       </c>
       <c r="C24">
         <f ca="1">VLOOKUP(G24,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1674</v>
+        <v>1091</v>
       </c>
       <c r="D24">
-        <f ca="1">VLOOKUP(H24,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1773</v>
+        <f ca="1">VLOOKUP(H24,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>56</v>
       </c>
       <c r="E24" s="1">
         <v>46316</v>
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="G24">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="H24">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I24" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1508, 1674, 1773, '2026-10-21', 2),</v>
+        <v>(1508, 1091, 56, '2026-10-21', 72),</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1439,30 +1667,30 @@
       </c>
       <c r="C25">
         <f ca="1">VLOOKUP(G25,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>346</v>
+        <v>1520</v>
       </c>
       <c r="D25">
-        <f ca="1">VLOOKUP(H25,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>346</v>
+        <f ca="1">VLOOKUP(H25,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>1953</v>
       </c>
       <c r="E25" s="1">
         <v>46358</v>
       </c>
       <c r="F25">
         <f t="shared" ca="1" si="0"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G25">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H25">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1734, 346, 346, '2026-12-02', 78),</v>
+        <v>(1734, 1520, 1953, '2026-12-02', 79),</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1474,22 +1702,22 @@
       </c>
       <c r="C26">
         <f ca="1">VLOOKUP(G26,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>1773</v>
+        <v>723</v>
       </c>
       <c r="D26">
-        <f ca="1">VLOOKUP(H26,[1]case!$A$2:$B$26,2,FALSE)</f>
-        <v>717</v>
+        <f ca="1">VLOOKUP(H26,[2]doctor!$A$2:$B$26,2,FALSE)</f>
+        <v>1165</v>
       </c>
       <c r="E26" s="1">
         <v>46385</v>
       </c>
       <c r="F26">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="G26">
         <f t="shared" ca="1" si="1"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H26">
         <f t="shared" ca="1" si="1"/>
@@ -1497,10 +1725,13 @@
       </c>
       <c r="I26" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(802, 1773, 717, '2026-12-29', 76),</v>
+        <v>(802, 723, 1165, '2026-12-29', 47),</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>